--- a/data/EZ_10y_dens.xlsx
+++ b/data/EZ_10y_dens.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="3846" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="3909" uniqueCount="189">
   <si>
     <t>date</t>
   </si>
@@ -567,6 +567,15 @@
     <t>2026-02-16</t>
   </si>
   <si>
+    <t>2026-03-02</t>
+  </si>
+  <si>
+    <t>2026-04-01</t>
+  </si>
+  <si>
+    <t>2026-05-07</t>
+  </si>
+  <si>
     <t>support</t>
   </si>
   <si>
@@ -616,7 +625,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C3844"/>
+  <dimension ref="A1:C3907"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -624,10 +633,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="C1" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
     </row>
     <row r="2">
@@ -42903,6 +42912,699 @@
         <v>0.0076608899575155709</v>
       </c>
     </row>
+    <row r="3845">
+      <c r="A3845" t="s">
+        <v>184</v>
+      </c>
+      <c r="B3845" s="1">
+        <v>-0.030000000000000009</v>
+      </c>
+      <c r="C3845" s="1">
+        <v>0.0001537893387068369</v>
+      </c>
+    </row>
+    <row r="3846">
+      <c r="A3846" t="s">
+        <v>184</v>
+      </c>
+      <c r="B3846" s="1">
+        <v>-0.025000000000000008</v>
+      </c>
+      <c r="C3846" s="1">
+        <v>0.00014735009423780403</v>
+      </c>
+    </row>
+    <row r="3847">
+      <c r="A3847" t="s">
+        <v>184</v>
+      </c>
+      <c r="B3847" s="1">
+        <v>-0.020000000000000007</v>
+      </c>
+      <c r="C3847" s="1">
+        <v>0.00030684476480699629</v>
+      </c>
+    </row>
+    <row r="3848">
+      <c r="A3848" t="s">
+        <v>184</v>
+      </c>
+      <c r="B3848" s="1">
+        <v>-0.015000000000000006</v>
+      </c>
+      <c r="C3848" s="1">
+        <v>0.00066863827941398624</v>
+      </c>
+    </row>
+    <row r="3849">
+      <c r="A3849" t="s">
+        <v>184</v>
+      </c>
+      <c r="B3849" s="1">
+        <v>-0.010000000000000005</v>
+      </c>
+      <c r="C3849" s="1">
+        <v>0.0015424387473144154</v>
+      </c>
+    </row>
+    <row r="3850">
+      <c r="A3850" t="s">
+        <v>184</v>
+      </c>
+      <c r="B3850" s="1">
+        <v>-0.0050000000000000053</v>
+      </c>
+      <c r="C3850" s="1">
+        <v>0.0038662268939140057</v>
+      </c>
+    </row>
+    <row r="3851">
+      <c r="A3851" t="s">
+        <v>184</v>
+      </c>
+      <c r="B3851" s="1">
+        <v>0</v>
+      </c>
+      <c r="C3851" s="1">
+        <v>0.010404285987676004</v>
+      </c>
+    </row>
+    <row r="3852">
+      <c r="A3852" t="s">
+        <v>184</v>
+      </c>
+      <c r="B3852" s="1">
+        <v>0.0050000000000000001</v>
+      </c>
+      <c r="C3852" s="1">
+        <v>0.029353263426112459</v>
+      </c>
+    </row>
+    <row r="3853">
+      <c r="A3853" t="s">
+        <v>184</v>
+      </c>
+      <c r="B3853" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="C3853" s="1">
+        <v>0.079516103081301873</v>
+      </c>
+    </row>
+    <row r="3854">
+      <c r="A3854" t="s">
+        <v>184</v>
+      </c>
+      <c r="B3854" s="1">
+        <v>0.014999999999999999</v>
+      </c>
+      <c r="C3854" s="1">
+        <v>0.17003140900705102</v>
+      </c>
+    </row>
+    <row r="3855">
+      <c r="A3855" t="s">
+        <v>184</v>
+      </c>
+      <c r="B3855" s="1">
+        <v>0.02</v>
+      </c>
+      <c r="C3855" s="1">
+        <v>0.23038681373902742</v>
+      </c>
+    </row>
+    <row r="3856">
+      <c r="A3856" t="s">
+        <v>184</v>
+      </c>
+      <c r="B3856" s="1">
+        <v>0.025000000000000001</v>
+      </c>
+      <c r="C3856" s="1">
+        <v>0.19351426588957774</v>
+      </c>
+    </row>
+    <row r="3857">
+      <c r="A3857" t="s">
+        <v>184</v>
+      </c>
+      <c r="B3857" s="1">
+        <v>0.030000000000000002</v>
+      </c>
+      <c r="C3857" s="1">
+        <v>0.12097976821358079</v>
+      </c>
+    </row>
+    <row r="3858">
+      <c r="A3858" t="s">
+        <v>184</v>
+      </c>
+      <c r="B3858" s="1">
+        <v>0.035000000000000003</v>
+      </c>
+      <c r="C3858" s="1">
+        <v>0.067640380082329948</v>
+      </c>
+    </row>
+    <row r="3859">
+      <c r="A3859" t="s">
+        <v>184</v>
+      </c>
+      <c r="B3859" s="1">
+        <v>0.040000000000000001</v>
+      </c>
+      <c r="C3859" s="1">
+        <v>0.037227347093703782</v>
+      </c>
+    </row>
+    <row r="3860">
+      <c r="A3860" t="s">
+        <v>184</v>
+      </c>
+      <c r="B3860" s="1">
+        <v>0.044999999999999998</v>
+      </c>
+      <c r="C3860" s="1">
+        <v>0.020928834021559612</v>
+      </c>
+    </row>
+    <row r="3861">
+      <c r="A3861" t="s">
+        <v>184</v>
+      </c>
+      <c r="B3861" s="1">
+        <v>0.049999999999999996</v>
+      </c>
+      <c r="C3861" s="1">
+        <v>0.012156137264193354</v>
+      </c>
+    </row>
+    <row r="3862">
+      <c r="A3862" t="s">
+        <v>184</v>
+      </c>
+      <c r="B3862" s="1">
+        <v>0.054999999999999993</v>
+      </c>
+      <c r="C3862" s="1">
+        <v>0.0073069397625283652</v>
+      </c>
+    </row>
+    <row r="3863">
+      <c r="A3863" t="s">
+        <v>184</v>
+      </c>
+      <c r="B3863" s="1">
+        <v>0.059999999999999991</v>
+      </c>
+      <c r="C3863" s="1">
+        <v>0.0045372981074161944</v>
+      </c>
+    </row>
+    <row r="3864">
+      <c r="A3864" t="s">
+        <v>184</v>
+      </c>
+      <c r="B3864" s="1">
+        <v>0.064999999999999988</v>
+      </c>
+      <c r="C3864" s="1">
+        <v>0.0029024503170568673</v>
+      </c>
+    </row>
+    <row r="3865">
+      <c r="A3865" t="s">
+        <v>184</v>
+      </c>
+      <c r="B3865" s="1">
+        <v>0.069999999999999993</v>
+      </c>
+      <c r="C3865" s="1">
+        <v>0.0064294158884903307</v>
+      </c>
+    </row>
+    <row r="3866">
+      <c r="A3866" t="s">
+        <v>185</v>
+      </c>
+      <c r="B3866" s="1">
+        <v>-0.030000000000000009</v>
+      </c>
+      <c r="C3866" s="1">
+        <v>0.00016394330258525562</v>
+      </c>
+    </row>
+    <row r="3867">
+      <c r="A3867" t="s">
+        <v>185</v>
+      </c>
+      <c r="B3867" s="1">
+        <v>-0.025000000000000008</v>
+      </c>
+      <c r="C3867" s="1">
+        <v>0.00013926145967786528</v>
+      </c>
+    </row>
+    <row r="3868">
+      <c r="A3868" t="s">
+        <v>185</v>
+      </c>
+      <c r="B3868" s="1">
+        <v>-0.020000000000000007</v>
+      </c>
+      <c r="C3868" s="1">
+        <v>0.00027292648613897342</v>
+      </c>
+    </row>
+    <row r="3869">
+      <c r="A3869" t="s">
+        <v>185</v>
+      </c>
+      <c r="B3869" s="1">
+        <v>-0.015000000000000006</v>
+      </c>
+      <c r="C3869" s="1">
+        <v>0.00055730759761583371</v>
+      </c>
+    </row>
+    <row r="3870">
+      <c r="A3870" t="s">
+        <v>185</v>
+      </c>
+      <c r="B3870" s="1">
+        <v>-0.010000000000000005</v>
+      </c>
+      <c r="C3870" s="1">
+        <v>0.0011988324298884685</v>
+      </c>
+    </row>
+    <row r="3871">
+      <c r="A3871" t="s">
+        <v>185</v>
+      </c>
+      <c r="B3871" s="1">
+        <v>-0.0050000000000000053</v>
+      </c>
+      <c r="C3871" s="1">
+        <v>0.0027978988316117769</v>
+      </c>
+    </row>
+    <row r="3872">
+      <c r="A3872" t="s">
+        <v>185</v>
+      </c>
+      <c r="B3872" s="1">
+        <v>0</v>
+      </c>
+      <c r="C3872" s="1">
+        <v>0.0070282310364193808</v>
+      </c>
+    </row>
+    <row r="3873">
+      <c r="A3873" t="s">
+        <v>185</v>
+      </c>
+      <c r="B3873" s="1">
+        <v>0.0050000000000000001</v>
+      </c>
+      <c r="C3873" s="1">
+        <v>0.018884025566041324</v>
+      </c>
+    </row>
+    <row r="3874">
+      <c r="A3874" t="s">
+        <v>185</v>
+      </c>
+      <c r="B3874" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="C3874" s="1">
+        <v>0.051843735433708141</v>
+      </c>
+    </row>
+    <row r="3875">
+      <c r="A3875" t="s">
+        <v>185</v>
+      </c>
+      <c r="B3875" s="1">
+        <v>0.014999999999999999</v>
+      </c>
+      <c r="C3875" s="1">
+        <v>0.12653778586974782</v>
+      </c>
+    </row>
+    <row r="3876">
+      <c r="A3876" t="s">
+        <v>185</v>
+      </c>
+      <c r="B3876" s="1">
+        <v>0.02</v>
+      </c>
+      <c r="C3876" s="1">
+        <v>0.21590015593170564</v>
+      </c>
+    </row>
+    <row r="3877">
+      <c r="A3877" t="s">
+        <v>185</v>
+      </c>
+      <c r="B3877" s="1">
+        <v>0.025000000000000001</v>
+      </c>
+      <c r="C3877" s="1">
+        <v>0.22136735466343524</v>
+      </c>
+    </row>
+    <row r="3878">
+      <c r="A3878" t="s">
+        <v>185</v>
+      </c>
+      <c r="B3878" s="1">
+        <v>0.030000000000000002</v>
+      </c>
+      <c r="C3878" s="1">
+        <v>0.15204622879528853</v>
+      </c>
+    </row>
+    <row r="3879">
+      <c r="A3879" t="s">
+        <v>185</v>
+      </c>
+      <c r="B3879" s="1">
+        <v>0.035000000000000003</v>
+      </c>
+      <c r="C3879" s="1">
+        <v>0.086826288699668019</v>
+      </c>
+    </row>
+    <row r="3880">
+      <c r="A3880" t="s">
+        <v>185</v>
+      </c>
+      <c r="B3880" s="1">
+        <v>0.040000000000000001</v>
+      </c>
+      <c r="C3880" s="1">
+        <v>0.04745018278217341</v>
+      </c>
+    </row>
+    <row r="3881">
+      <c r="A3881" t="s">
+        <v>185</v>
+      </c>
+      <c r="B3881" s="1">
+        <v>0.044999999999999998</v>
+      </c>
+      <c r="C3881" s="1">
+        <v>0.026303350569096214</v>
+      </c>
+    </row>
+    <row r="3882">
+      <c r="A3882" t="s">
+        <v>185</v>
+      </c>
+      <c r="B3882" s="1">
+        <v>0.049999999999999996</v>
+      </c>
+      <c r="C3882" s="1">
+        <v>0.015067489891776548</v>
+      </c>
+    </row>
+    <row r="3883">
+      <c r="A3883" t="s">
+        <v>185</v>
+      </c>
+      <c r="B3883" s="1">
+        <v>0.054999999999999993</v>
+      </c>
+      <c r="C3883" s="1">
+        <v>0.0089514415967377504</v>
+      </c>
+    </row>
+    <row r="3884">
+      <c r="A3884" t="s">
+        <v>185</v>
+      </c>
+      <c r="B3884" s="1">
+        <v>0.059999999999999991</v>
+      </c>
+      <c r="C3884" s="1">
+        <v>0.0055067790694390316</v>
+      </c>
+    </row>
+    <row r="3885">
+      <c r="A3885" t="s">
+        <v>185</v>
+      </c>
+      <c r="B3885" s="1">
+        <v>0.064999999999999988</v>
+      </c>
+      <c r="C3885" s="1">
+        <v>0.0034971963744575584</v>
+      </c>
+    </row>
+    <row r="3886">
+      <c r="A3886" t="s">
+        <v>185</v>
+      </c>
+      <c r="B3886" s="1">
+        <v>0.069999999999999993</v>
+      </c>
+      <c r="C3886" s="1">
+        <v>0.0076595836127872907</v>
+      </c>
+    </row>
+    <row r="3887">
+      <c r="A3887" t="s">
+        <v>186</v>
+      </c>
+      <c r="B3887" s="1">
+        <v>-0.030000000000000009</v>
+      </c>
+      <c r="C3887" s="1">
+        <v>0.00022770907732115245</v>
+      </c>
+    </row>
+    <row r="3888">
+      <c r="A3888" t="s">
+        <v>186</v>
+      </c>
+      <c r="B3888" s="1">
+        <v>-0.025000000000000008</v>
+      </c>
+      <c r="C3888" s="1">
+        <v>0.00018661520310663457</v>
+      </c>
+    </row>
+    <row r="3889">
+      <c r="A3889" t="s">
+        <v>186</v>
+      </c>
+      <c r="B3889" s="1">
+        <v>-0.020000000000000007</v>
+      </c>
+      <c r="C3889" s="1">
+        <v>0.00035885859667060646</v>
+      </c>
+    </row>
+    <row r="3890">
+      <c r="A3890" t="s">
+        <v>186</v>
+      </c>
+      <c r="B3890" s="1">
+        <v>-0.015000000000000006</v>
+      </c>
+      <c r="C3890" s="1">
+        <v>0.00071711805392215254</v>
+      </c>
+    </row>
+    <row r="3891">
+      <c r="A3891" t="s">
+        <v>186</v>
+      </c>
+      <c r="B3891" s="1">
+        <v>-0.010000000000000005</v>
+      </c>
+      <c r="C3891" s="1">
+        <v>0.0015039462118486184</v>
+      </c>
+    </row>
+    <row r="3892">
+      <c r="A3892" t="s">
+        <v>186</v>
+      </c>
+      <c r="B3892" s="1">
+        <v>-0.0050000000000000053</v>
+      </c>
+      <c r="C3892" s="1">
+        <v>0.0033976764738748839</v>
+      </c>
+    </row>
+    <row r="3893">
+      <c r="A3893" t="s">
+        <v>186</v>
+      </c>
+      <c r="B3893" s="1">
+        <v>0</v>
+      </c>
+      <c r="C3893" s="1">
+        <v>0.0081888436865527967</v>
+      </c>
+    </row>
+    <row r="3894">
+      <c r="A3894" t="s">
+        <v>186</v>
+      </c>
+      <c r="B3894" s="1">
+        <v>0.0050000000000000001</v>
+      </c>
+      <c r="C3894" s="1">
+        <v>0.020865814894502319</v>
+      </c>
+    </row>
+    <row r="3895">
+      <c r="A3895" t="s">
+        <v>186</v>
+      </c>
+      <c r="B3895" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="C3895" s="1">
+        <v>0.053692909406656698</v>
+      </c>
+    </row>
+    <row r="3896">
+      <c r="A3896" t="s">
+        <v>186</v>
+      </c>
+      <c r="B3896" s="1">
+        <v>0.014999999999999999</v>
+      </c>
+      <c r="C3896" s="1">
+        <v>0.12300750255631725</v>
+      </c>
+    </row>
+    <row r="3897">
+      <c r="A3897" t="s">
+        <v>186</v>
+      </c>
+      <c r="B3897" s="1">
+        <v>0.02</v>
+      </c>
+      <c r="C3897" s="1">
+        <v>0.20372741667906213</v>
+      </c>
+    </row>
+    <row r="3898">
+      <c r="A3898" t="s">
+        <v>186</v>
+      </c>
+      <c r="B3898" s="1">
+        <v>0.025000000000000001</v>
+      </c>
+      <c r="C3898" s="1">
+        <v>0.21303088680508722</v>
+      </c>
+    </row>
+    <row r="3899">
+      <c r="A3899" t="s">
+        <v>186</v>
+      </c>
+      <c r="B3899" s="1">
+        <v>0.030000000000000002</v>
+      </c>
+      <c r="C3899" s="1">
+        <v>0.15285868125219429</v>
+      </c>
+    </row>
+    <row r="3900">
+      <c r="A3900" t="s">
+        <v>186</v>
+      </c>
+      <c r="B3900" s="1">
+        <v>0.035000000000000003</v>
+      </c>
+      <c r="C3900" s="1">
+        <v>0.090904957544143419</v>
+      </c>
+    </row>
+    <row r="3901">
+      <c r="A3901" t="s">
+        <v>186</v>
+      </c>
+      <c r="B3901" s="1">
+        <v>0.040000000000000001</v>
+      </c>
+      <c r="C3901" s="1">
+        <v>0.051235364735996304</v>
+      </c>
+    </row>
+    <row r="3902">
+      <c r="A3902" t="s">
+        <v>186</v>
+      </c>
+      <c r="B3902" s="1">
+        <v>0.044999999999999998</v>
+      </c>
+      <c r="C3902" s="1">
+        <v>0.029071905775291781</v>
+      </c>
+    </row>
+    <row r="3903">
+      <c r="A3903" t="s">
+        <v>186</v>
+      </c>
+      <c r="B3903" s="1">
+        <v>0.049999999999999996</v>
+      </c>
+      <c r="C3903" s="1">
+        <v>0.016964835878977021</v>
+      </c>
+    </row>
+    <row r="3904">
+      <c r="A3904" t="s">
+        <v>186</v>
+      </c>
+      <c r="B3904" s="1">
+        <v>0.054999999999999993</v>
+      </c>
+      <c r="C3904" s="1">
+        <v>0.010236176725866032</v>
+      </c>
+    </row>
+    <row r="3905">
+      <c r="A3905" t="s">
+        <v>186</v>
+      </c>
+      <c r="B3905" s="1">
+        <v>0.059999999999999991</v>
+      </c>
+      <c r="C3905" s="1">
+        <v>0.006383034053329498</v>
+      </c>
+    </row>
+    <row r="3906">
+      <c r="A3906" t="s">
+        <v>186</v>
+      </c>
+      <c r="B3906" s="1">
+        <v>0.064999999999999988</v>
+      </c>
+      <c r="C3906" s="1">
+        <v>0.004103523240759588</v>
+      </c>
+    </row>
+    <row r="3907">
+      <c r="A3907" t="s">
+        <v>186</v>
+      </c>
+      <c r="B3907" s="1">
+        <v>0.069999999999999993</v>
+      </c>
+      <c r="C3907" s="1">
+        <v>0.0093362231485196734</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>